--- a/wk4/pivot-tables.xlsx
+++ b/wk4/pivot-tables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop W11\working_folder\Personales\Upright\Data_Science\instructor-dab-sep-2026\wk4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jatin/Desktop/Learnings/Upright/Student_Repo/wk4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC4B49C9-A95C-4774-91C7-C5802A6846CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{371ED637-A120-C94D-AFD6-7EAEDAFD673C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="796" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-36420" yWindow="-3720" windowWidth="29400" windowHeight="17180" tabRatio="796" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -18,10 +18,22 @@
     <sheet name="Two-dimensional Pivot Table" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$F$214</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$F$1</definedName>
+    <definedName name="NativeTimeline_Date">#N/A</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="27" r:id="rId4"/>
+  </pivotCaches>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
+      <x14:workbookPr/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}">
+      <x15:timelineCacheRefs>
+        <x15:timelineCacheRef r:id="rId5"/>
+      </x15:timelineCacheRefs>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -38,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="679" uniqueCount="24">
   <si>
     <t>Country</t>
   </si>
@@ -105,6 +117,12 @@
   <si>
     <t>New Zealand</t>
   </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Sum of Amount</t>
+  </si>
 </sst>
 </file>
 
@@ -150,13 +168,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -172,6 +191,4743 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[pivot-tables.xlsx]Two-dimensional Pivot Table!PivotTable6</c:name>
+    <c:fmtId val="5"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Two-dimensional Pivot Table'!$B$1:$B$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Apple</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Two-dimensional Pivot Table'!$A$3:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Australia</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Canada</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>France</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Germany</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>United Kingdom</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>United States</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Two-dimensional Pivot Table'!$B$3:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>"$"#,##0</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="1">
+                  <c:v>521</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5605</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A288-7F4A-9856-A8F69529D9F7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Two-dimensional Pivot Table'!$C$1:$C$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Banana</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Two-dimensional Pivot Table'!$A$3:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Australia</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Canada</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>France</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Germany</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>United Kingdom</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>United States</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Two-dimensional Pivot Table'!$C$3:$C$9</c:f>
+              <c:numCache>
+                <c:formatCode>"$"#,##0</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="1">
+                  <c:v>6941</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8160</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-A288-7F4A-9856-A8F69529D9F7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Two-dimensional Pivot Table'!$D$1:$D$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Broccoli</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Two-dimensional Pivot Table'!$A$3:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Australia</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Canada</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>France</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Germany</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>United Kingdom</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>United States</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Two-dimensional Pivot Table'!$D$3:$D$9</c:f>
+              <c:numCache>
+                <c:formatCode>"$"#,##0</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>8891</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9630</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7231</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-A288-7F4A-9856-A8F69529D9F7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Two-dimensional Pivot Table'!$E$1:$E$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Orange</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Two-dimensional Pivot Table'!$A$3:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Australia</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Canada</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>France</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Germany</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>United Kingdom</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>United States</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Two-dimensional Pivot Table'!$E$3:$E$9</c:f>
+              <c:numCache>
+                <c:formatCode>"$"#,##0</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="5">
+                  <c:v>4514</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-A288-7F4A-9856-A8F69529D9F7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1565538304"/>
+        <c:axId val="1496397824"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1565538304"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1496397824"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1496397824"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="&quot;$&quot;#,##0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1565538304"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>215900</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>393700</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7FF45EFA-AC14-5973-6CA6-8CD81DF8A6A2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>203200</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer" Requires="tsle">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="5" name="Date">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0EADFF82-1EE6-07A2-82F5-EB5A966651EC}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2012/timeslicer">
+              <tsle:timeslicer xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer" name="Date"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5359400" y="5930900"/>
+              <a:ext cx="3340100" cy="1320800"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>Timeline: Works in Excel 2013 or higher. Do not move or resize.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Jatin Mistry" refreshedDate="46310.853277893519" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="213" xr:uid="{C216B1F3-2CD8-384C-8494-AAD7C1A4EB38}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:F214" sheet="Data"/>
+  </cacheSource>
+  <cacheFields count="6">
+    <cacheField name="Order ID" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="213" count="213">
+        <n v="1"/>
+        <n v="2"/>
+        <n v="3"/>
+        <n v="4"/>
+        <n v="5"/>
+        <n v="6"/>
+        <n v="7"/>
+        <n v="8"/>
+        <n v="9"/>
+        <n v="10"/>
+        <n v="11"/>
+        <n v="12"/>
+        <n v="13"/>
+        <n v="14"/>
+        <n v="15"/>
+        <n v="16"/>
+        <n v="17"/>
+        <n v="18"/>
+        <n v="19"/>
+        <n v="20"/>
+        <n v="21"/>
+        <n v="22"/>
+        <n v="23"/>
+        <n v="24"/>
+        <n v="25"/>
+        <n v="26"/>
+        <n v="27"/>
+        <n v="28"/>
+        <n v="29"/>
+        <n v="30"/>
+        <n v="31"/>
+        <n v="32"/>
+        <n v="33"/>
+        <n v="34"/>
+        <n v="35"/>
+        <n v="36"/>
+        <n v="37"/>
+        <n v="38"/>
+        <n v="39"/>
+        <n v="40"/>
+        <n v="41"/>
+        <n v="42"/>
+        <n v="43"/>
+        <n v="44"/>
+        <n v="45"/>
+        <n v="46"/>
+        <n v="47"/>
+        <n v="48"/>
+        <n v="49"/>
+        <n v="50"/>
+        <n v="51"/>
+        <n v="52"/>
+        <n v="53"/>
+        <n v="54"/>
+        <n v="55"/>
+        <n v="56"/>
+        <n v="57"/>
+        <n v="58"/>
+        <n v="59"/>
+        <n v="60"/>
+        <n v="61"/>
+        <n v="62"/>
+        <n v="63"/>
+        <n v="64"/>
+        <n v="65"/>
+        <n v="66"/>
+        <n v="67"/>
+        <n v="68"/>
+        <n v="69"/>
+        <n v="70"/>
+        <n v="71"/>
+        <n v="72"/>
+        <n v="73"/>
+        <n v="74"/>
+        <n v="75"/>
+        <n v="76"/>
+        <n v="77"/>
+        <n v="78"/>
+        <n v="79"/>
+        <n v="80"/>
+        <n v="81"/>
+        <n v="82"/>
+        <n v="83"/>
+        <n v="84"/>
+        <n v="85"/>
+        <n v="86"/>
+        <n v="87"/>
+        <n v="88"/>
+        <n v="89"/>
+        <n v="90"/>
+        <n v="91"/>
+        <n v="92"/>
+        <n v="93"/>
+        <n v="94"/>
+        <n v="95"/>
+        <n v="96"/>
+        <n v="97"/>
+        <n v="98"/>
+        <n v="99"/>
+        <n v="100"/>
+        <n v="101"/>
+        <n v="102"/>
+        <n v="103"/>
+        <n v="104"/>
+        <n v="105"/>
+        <n v="106"/>
+        <n v="107"/>
+        <n v="108"/>
+        <n v="109"/>
+        <n v="110"/>
+        <n v="111"/>
+        <n v="112"/>
+        <n v="113"/>
+        <n v="114"/>
+        <n v="115"/>
+        <n v="116"/>
+        <n v="117"/>
+        <n v="118"/>
+        <n v="119"/>
+        <n v="120"/>
+        <n v="121"/>
+        <n v="122"/>
+        <n v="123"/>
+        <n v="124"/>
+        <n v="125"/>
+        <n v="126"/>
+        <n v="127"/>
+        <n v="128"/>
+        <n v="129"/>
+        <n v="130"/>
+        <n v="131"/>
+        <n v="132"/>
+        <n v="133"/>
+        <n v="134"/>
+        <n v="135"/>
+        <n v="136"/>
+        <n v="137"/>
+        <n v="138"/>
+        <n v="139"/>
+        <n v="140"/>
+        <n v="141"/>
+        <n v="142"/>
+        <n v="143"/>
+        <n v="144"/>
+        <n v="145"/>
+        <n v="146"/>
+        <n v="147"/>
+        <n v="148"/>
+        <n v="149"/>
+        <n v="150"/>
+        <n v="151"/>
+        <n v="152"/>
+        <n v="153"/>
+        <n v="154"/>
+        <n v="155"/>
+        <n v="156"/>
+        <n v="157"/>
+        <n v="158"/>
+        <n v="159"/>
+        <n v="160"/>
+        <n v="161"/>
+        <n v="162"/>
+        <n v="163"/>
+        <n v="164"/>
+        <n v="165"/>
+        <n v="166"/>
+        <n v="167"/>
+        <n v="168"/>
+        <n v="169"/>
+        <n v="170"/>
+        <n v="171"/>
+        <n v="172"/>
+        <n v="173"/>
+        <n v="174"/>
+        <n v="175"/>
+        <n v="176"/>
+        <n v="177"/>
+        <n v="178"/>
+        <n v="179"/>
+        <n v="180"/>
+        <n v="181"/>
+        <n v="182"/>
+        <n v="183"/>
+        <n v="184"/>
+        <n v="185"/>
+        <n v="186"/>
+        <n v="187"/>
+        <n v="188"/>
+        <n v="189"/>
+        <n v="190"/>
+        <n v="191"/>
+        <n v="192"/>
+        <n v="193"/>
+        <n v="194"/>
+        <n v="195"/>
+        <n v="196"/>
+        <n v="197"/>
+        <n v="198"/>
+        <n v="199"/>
+        <n v="200"/>
+        <n v="201"/>
+        <n v="202"/>
+        <n v="203"/>
+        <n v="204"/>
+        <n v="205"/>
+        <n v="206"/>
+        <n v="207"/>
+        <n v="208"/>
+        <n v="209"/>
+        <n v="210"/>
+        <n v="211"/>
+        <n v="212"/>
+        <n v="213"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Product" numFmtId="0">
+      <sharedItems count="7">
+        <s v="Carrots"/>
+        <s v="Broccoli"/>
+        <s v="Banana"/>
+        <s v="Beans"/>
+        <s v="Orange"/>
+        <s v="Apple"/>
+        <s v="Mango"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Category" numFmtId="0">
+      <sharedItems count="2">
+        <s v="Vegetables"/>
+        <s v="Fruit"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Amount" numFmtId="164">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="107" maxValue="9990"/>
+    </cacheField>
+    <cacheField name="Date" numFmtId="14">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2024-01-06T00:00:00" maxDate="2024-12-31T00:00:00" count="150">
+        <d v="2024-01-06T00:00:00"/>
+        <d v="2024-01-07T00:00:00"/>
+        <d v="2024-01-08T00:00:00"/>
+        <d v="2024-01-10T00:00:00"/>
+        <d v="2024-01-11T00:00:00"/>
+        <d v="2024-01-16T00:00:00"/>
+        <d v="2024-01-18T00:00:00"/>
+        <d v="2024-01-20T00:00:00"/>
+        <d v="2024-01-22T00:00:00"/>
+        <d v="2024-01-24T00:00:00"/>
+        <d v="2024-01-27T00:00:00"/>
+        <d v="2024-01-28T00:00:00"/>
+        <d v="2024-01-30T00:00:00"/>
+        <d v="2024-02-02T00:00:00"/>
+        <d v="2024-02-04T00:00:00"/>
+        <d v="2024-02-11T00:00:00"/>
+        <d v="2024-02-14T00:00:00"/>
+        <d v="2024-02-17T00:00:00"/>
+        <d v="2024-02-18T00:00:00"/>
+        <d v="2024-02-20T00:00:00"/>
+        <d v="2024-02-21T00:00:00"/>
+        <d v="2024-02-22T00:00:00"/>
+        <d v="2024-02-23T00:00:00"/>
+        <d v="2024-02-29T00:00:00"/>
+        <d v="2024-03-01T00:00:00"/>
+        <d v="2024-03-04T00:00:00"/>
+        <d v="2024-03-05T00:00:00"/>
+        <d v="2024-03-15T00:00:00"/>
+        <d v="2024-03-16T00:00:00"/>
+        <d v="2024-03-19T00:00:00"/>
+        <d v="2024-03-21T00:00:00"/>
+        <d v="2024-03-22T00:00:00"/>
+        <d v="2024-03-23T00:00:00"/>
+        <d v="2024-03-24T00:00:00"/>
+        <d v="2024-03-26T00:00:00"/>
+        <d v="2024-03-29T00:00:00"/>
+        <d v="2024-03-30T00:00:00"/>
+        <d v="2024-04-01T00:00:00"/>
+        <d v="2024-04-03T00:00:00"/>
+        <d v="2024-04-06T00:00:00"/>
+        <d v="2024-04-12T00:00:00"/>
+        <d v="2024-04-17T00:00:00"/>
+        <d v="2024-04-18T00:00:00"/>
+        <d v="2024-04-21T00:00:00"/>
+        <d v="2024-04-22T00:00:00"/>
+        <d v="2024-04-23T00:00:00"/>
+        <d v="2024-04-25T00:00:00"/>
+        <d v="2024-04-27T00:00:00"/>
+        <d v="2024-04-30T00:00:00"/>
+        <d v="2024-05-01T00:00:00"/>
+        <d v="2024-05-02T00:00:00"/>
+        <d v="2024-05-03T00:00:00"/>
+        <d v="2024-05-05T00:00:00"/>
+        <d v="2024-05-06T00:00:00"/>
+        <d v="2024-05-08T00:00:00"/>
+        <d v="2024-05-12T00:00:00"/>
+        <d v="2024-05-14T00:00:00"/>
+        <d v="2024-05-15T00:00:00"/>
+        <d v="2024-05-16T00:00:00"/>
+        <d v="2024-05-18T00:00:00"/>
+        <d v="2024-05-19T00:00:00"/>
+        <d v="2024-05-20T00:00:00"/>
+        <d v="2024-05-22T00:00:00"/>
+        <d v="2024-05-23T00:00:00"/>
+        <d v="2024-05-25T00:00:00"/>
+        <d v="2024-05-26T00:00:00"/>
+        <d v="2024-05-27T00:00:00"/>
+        <d v="2024-05-28T00:00:00"/>
+        <d v="2024-05-29T00:00:00"/>
+        <d v="2024-05-30T00:00:00"/>
+        <d v="2024-06-04T00:00:00"/>
+        <d v="2024-06-10T00:00:00"/>
+        <d v="2024-06-11T00:00:00"/>
+        <d v="2024-06-20T00:00:00"/>
+        <d v="2024-06-23T00:00:00"/>
+        <d v="2024-06-25T00:00:00"/>
+        <d v="2024-06-26T00:00:00"/>
+        <d v="2024-06-27T00:00:00"/>
+        <d v="2024-07-02T00:00:00"/>
+        <d v="2024-07-05T00:00:00"/>
+        <d v="2024-07-07T00:00:00"/>
+        <d v="2024-07-11T00:00:00"/>
+        <d v="2024-07-13T00:00:00"/>
+        <d v="2024-07-20T00:00:00"/>
+        <d v="2024-07-22T00:00:00"/>
+        <d v="2024-07-23T00:00:00"/>
+        <d v="2024-07-25T00:00:00"/>
+        <d v="2024-07-28T00:00:00"/>
+        <d v="2024-07-29T00:00:00"/>
+        <d v="2024-07-30T00:00:00"/>
+        <d v="2024-07-31T00:00:00"/>
+        <d v="2024-08-01T00:00:00"/>
+        <d v="2024-08-03T00:00:00"/>
+        <d v="2024-08-12T00:00:00"/>
+        <d v="2024-08-13T00:00:00"/>
+        <d v="2024-08-19T00:00:00"/>
+        <d v="2024-08-23T00:00:00"/>
+        <d v="2024-08-24T00:00:00"/>
+        <d v="2024-08-25T00:00:00"/>
+        <d v="2024-08-27T00:00:00"/>
+        <d v="2024-08-28T00:00:00"/>
+        <d v="2024-08-29T00:00:00"/>
+        <d v="2024-09-01T00:00:00"/>
+        <d v="2024-09-02T00:00:00"/>
+        <d v="2024-09-05T00:00:00"/>
+        <d v="2024-09-07T00:00:00"/>
+        <d v="2024-09-08T00:00:00"/>
+        <d v="2024-09-09T00:00:00"/>
+        <d v="2024-09-11T00:00:00"/>
+        <d v="2024-09-15T00:00:00"/>
+        <d v="2024-09-18T00:00:00"/>
+        <d v="2024-09-19T00:00:00"/>
+        <d v="2024-09-20T00:00:00"/>
+        <d v="2024-09-25T00:00:00"/>
+        <d v="2024-09-26T00:00:00"/>
+        <d v="2024-09-27T00:00:00"/>
+        <d v="2024-09-29T00:00:00"/>
+        <d v="2024-10-03T00:00:00"/>
+        <d v="2024-10-04T00:00:00"/>
+        <d v="2024-10-07T00:00:00"/>
+        <d v="2024-10-10T00:00:00"/>
+        <d v="2024-10-16T00:00:00"/>
+        <d v="2024-10-23T00:00:00"/>
+        <d v="2024-10-25T00:00:00"/>
+        <d v="2024-10-26T00:00:00"/>
+        <d v="2024-11-02T00:00:00"/>
+        <d v="2024-11-03T00:00:00"/>
+        <d v="2024-11-09T00:00:00"/>
+        <d v="2024-11-12T00:00:00"/>
+        <d v="2024-11-15T00:00:00"/>
+        <d v="2024-11-25T00:00:00"/>
+        <d v="2024-11-26T00:00:00"/>
+        <d v="2024-11-28T00:00:00"/>
+        <d v="2024-11-29T00:00:00"/>
+        <d v="2024-11-30T00:00:00"/>
+        <d v="2024-12-02T00:00:00"/>
+        <d v="2024-12-04T00:00:00"/>
+        <d v="2024-12-05T00:00:00"/>
+        <d v="2024-12-06T00:00:00"/>
+        <d v="2024-12-12T00:00:00"/>
+        <d v="2024-12-15T00:00:00"/>
+        <d v="2024-12-16T00:00:00"/>
+        <d v="2024-12-18T00:00:00"/>
+        <d v="2024-12-19T00:00:00"/>
+        <d v="2024-12-20T00:00:00"/>
+        <d v="2024-12-22T00:00:00"/>
+        <d v="2024-12-25T00:00:00"/>
+        <d v="2024-12-28T00:00:00"/>
+        <d v="2024-12-29T00:00:00"/>
+        <d v="2024-12-30T00:00:00"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Country" numFmtId="0">
+      <sharedItems count="7">
+        <s v="United States"/>
+        <s v="United Kingdom"/>
+        <s v="Canada"/>
+        <s v="Germany"/>
+        <s v="Australia"/>
+        <s v="New Zealand"/>
+        <s v="France"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition pivotCacheId="923316403"/>
+    </ext>
+    <ext xmlns:xlpdsc="http://schemas.microsoft.com/office/spreadsheetml/2026/pivotDataSourceClean" uri="{F4336242-56EE-4DD3-A5F7-E900642BF6E9}">
+      <xlpdsc:dataSourceClean>1</xlpdsc:dataSourceClean>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="213">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="4270"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="8239"/>
+    <x v="1"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="617"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="8384"/>
+    <x v="3"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="2626"/>
+    <x v="3"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="4"/>
+    <x v="1"/>
+    <n v="3610"/>
+    <x v="4"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="9062"/>
+    <x v="4"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="6906"/>
+    <x v="5"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="2417"/>
+    <x v="5"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="7431"/>
+    <x v="5"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="8250"/>
+    <x v="5"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="7012"/>
+    <x v="6"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1903"/>
+    <x v="7"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="13"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="2824"/>
+    <x v="8"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="14"/>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="6946"/>
+    <x v="9"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="15"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="2320"/>
+    <x v="10"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="16"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="2116"/>
+    <x v="11"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="17"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="1135"/>
+    <x v="12"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="18"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="3595"/>
+    <x v="12"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="19"/>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="1161"/>
+    <x v="13"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="20"/>
+    <x v="4"/>
+    <x v="1"/>
+    <n v="2256"/>
+    <x v="14"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="21"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="1004"/>
+    <x v="15"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="22"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="3642"/>
+    <x v="16"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="23"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="4582"/>
+    <x v="17"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="24"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="3559"/>
+    <x v="17"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="25"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="5154"/>
+    <x v="17"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="26"/>
+    <x v="6"/>
+    <x v="1"/>
+    <n v="7388"/>
+    <x v="18"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="27"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="7163"/>
+    <x v="18"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="28"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="5101"/>
+    <x v="19"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="29"/>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="7602"/>
+    <x v="20"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="30"/>
+    <x v="6"/>
+    <x v="1"/>
+    <n v="1641"/>
+    <x v="21"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="31"/>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="8892"/>
+    <x v="22"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="32"/>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="2060"/>
+    <x v="23"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="33"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="1557"/>
+    <x v="23"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="34"/>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="6509"/>
+    <x v="24"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="35"/>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="5718"/>
+    <x v="25"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="36"/>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="7655"/>
+    <x v="26"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="37"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="9116"/>
+    <x v="26"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="38"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="2795"/>
+    <x v="27"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="39"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="5084"/>
+    <x v="27"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="40"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="8941"/>
+    <x v="27"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="41"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="5341"/>
+    <x v="28"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="42"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="135"/>
+    <x v="29"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="43"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="9400"/>
+    <x v="29"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="44"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="6045"/>
+    <x v="30"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="45"/>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="5820"/>
+    <x v="31"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="46"/>
+    <x v="4"/>
+    <x v="1"/>
+    <n v="8887"/>
+    <x v="32"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="47"/>
+    <x v="4"/>
+    <x v="1"/>
+    <n v="6982"/>
+    <x v="33"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="48"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="4029"/>
+    <x v="34"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="49"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="3665"/>
+    <x v="34"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="50"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="4781"/>
+    <x v="35"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="51"/>
+    <x v="6"/>
+    <x v="1"/>
+    <n v="3663"/>
+    <x v="36"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="52"/>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="6331"/>
+    <x v="37"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="53"/>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="4364"/>
+    <x v="37"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="54"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="607"/>
+    <x v="38"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="55"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="1054"/>
+    <x v="39"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="56"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="7659"/>
+    <x v="39"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="57"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="277"/>
+    <x v="40"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="58"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="235"/>
+    <x v="41"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="59"/>
+    <x v="4"/>
+    <x v="1"/>
+    <n v="1113"/>
+    <x v="42"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="60"/>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="1128"/>
+    <x v="43"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="61"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="9231"/>
+    <x v="44"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="62"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="4387"/>
+    <x v="45"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="63"/>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="2763"/>
+    <x v="46"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="64"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="7898"/>
+    <x v="47"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="65"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="2427"/>
+    <x v="48"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="66"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="8663"/>
+    <x v="49"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="67"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="2789"/>
+    <x v="49"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="68"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="4054"/>
+    <x v="50"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="69"/>
+    <x v="6"/>
+    <x v="1"/>
+    <n v="2262"/>
+    <x v="50"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="70"/>
+    <x v="6"/>
+    <x v="1"/>
+    <n v="5600"/>
+    <x v="50"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="71"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="5787"/>
+    <x v="51"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="72"/>
+    <x v="4"/>
+    <x v="1"/>
+    <n v="6295"/>
+    <x v="51"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="73"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="474"/>
+    <x v="52"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="74"/>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="4325"/>
+    <x v="52"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="75"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="592"/>
+    <x v="53"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="76"/>
+    <x v="4"/>
+    <x v="1"/>
+    <n v="4330"/>
+    <x v="54"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="77"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="9405"/>
+    <x v="54"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="78"/>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="7671"/>
+    <x v="54"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="79"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="5791"/>
+    <x v="54"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="80"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="6007"/>
+    <x v="55"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="81"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="5030"/>
+    <x v="56"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="82"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="6763"/>
+    <x v="56"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="83"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="4248"/>
+    <x v="57"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="84"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="9543"/>
+    <x v="58"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="85"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="2054"/>
+    <x v="58"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="86"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="7094"/>
+    <x v="58"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="87"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="6087"/>
+    <x v="59"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="88"/>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="4264"/>
+    <x v="60"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="89"/>
+    <x v="6"/>
+    <x v="1"/>
+    <n v="9333"/>
+    <x v="61"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="90"/>
+    <x v="6"/>
+    <x v="1"/>
+    <n v="8775"/>
+    <x v="62"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="91"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="2011"/>
+    <x v="63"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="92"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="5632"/>
+    <x v="64"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="93"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="4904"/>
+    <x v="64"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="94"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="1002"/>
+    <x v="64"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="95"/>
+    <x v="4"/>
+    <x v="1"/>
+    <n v="8141"/>
+    <x v="65"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="96"/>
+    <x v="4"/>
+    <x v="1"/>
+    <n v="3644"/>
+    <x v="65"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="97"/>
+    <x v="4"/>
+    <x v="1"/>
+    <n v="1380"/>
+    <x v="65"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="98"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="8354"/>
+    <x v="65"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="99"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="5182"/>
+    <x v="66"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="100"/>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="2193"/>
+    <x v="66"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="101"/>
+    <x v="6"/>
+    <x v="1"/>
+    <n v="3647"/>
+    <x v="67"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="102"/>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="4104"/>
+    <x v="67"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="103"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="7457"/>
+    <x v="67"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="104"/>
+    <x v="6"/>
+    <x v="1"/>
+    <n v="3767"/>
+    <x v="68"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="105"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="4685"/>
+    <x v="69"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="106"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="3917"/>
+    <x v="70"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="107"/>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="521"/>
+    <x v="70"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="108"/>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="5605"/>
+    <x v="71"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="109"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="9630"/>
+    <x v="72"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="110"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="6941"/>
+    <x v="73"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="111"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="7231"/>
+    <x v="73"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="112"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="8891"/>
+    <x v="74"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="113"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="107"/>
+    <x v="75"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="114"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="4243"/>
+    <x v="76"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="115"/>
+    <x v="4"/>
+    <x v="1"/>
+    <n v="4514"/>
+    <x v="77"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="116"/>
+    <x v="6"/>
+    <x v="1"/>
+    <n v="5480"/>
+    <x v="78"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="117"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="5002"/>
+    <x v="78"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="118"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="8530"/>
+    <x v="79"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="119"/>
+    <x v="4"/>
+    <x v="1"/>
+    <n v="4819"/>
+    <x v="80"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="120"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="6343"/>
+    <x v="81"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="121"/>
+    <x v="4"/>
+    <x v="1"/>
+    <n v="2318"/>
+    <x v="82"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="122"/>
+    <x v="4"/>
+    <x v="1"/>
+    <n v="220"/>
+    <x v="83"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="123"/>
+    <x v="4"/>
+    <x v="1"/>
+    <n v="6341"/>
+    <x v="83"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="124"/>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="330"/>
+    <x v="83"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="125"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="3027"/>
+    <x v="83"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="126"/>
+    <x v="4"/>
+    <x v="1"/>
+    <n v="850"/>
+    <x v="84"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="127"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="8986"/>
+    <x v="85"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="128"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="3800"/>
+    <x v="86"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="129"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="5751"/>
+    <x v="87"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="130"/>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="1704"/>
+    <x v="88"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="131"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="7966"/>
+    <x v="89"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="132"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="852"/>
+    <x v="90"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="133"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="8416"/>
+    <x v="90"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="134"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="7144"/>
+    <x v="91"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="135"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="7854"/>
+    <x v="91"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="136"/>
+    <x v="4"/>
+    <x v="1"/>
+    <n v="859"/>
+    <x v="92"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="137"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="8049"/>
+    <x v="93"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="138"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="2836"/>
+    <x v="94"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="139"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1743"/>
+    <x v="95"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="140"/>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="3844"/>
+    <x v="96"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="141"/>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="7490"/>
+    <x v="97"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="142"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="4483"/>
+    <x v="98"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="143"/>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="7333"/>
+    <x v="99"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="144"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="7654"/>
+    <x v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="145"/>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="3944"/>
+    <x v="101"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="146"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="5761"/>
+    <x v="101"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="147"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="6864"/>
+    <x v="102"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="148"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="4016"/>
+    <x v="102"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="149"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="1841"/>
+    <x v="103"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="150"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="424"/>
+    <x v="104"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="151"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="8765"/>
+    <x v="105"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="152"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="5583"/>
+    <x v="106"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="153"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="4390"/>
+    <x v="107"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="154"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="352"/>
+    <x v="107"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="155"/>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="8489"/>
+    <x v="108"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="156"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="7090"/>
+    <x v="108"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="157"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="7880"/>
+    <x v="109"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="158"/>
+    <x v="4"/>
+    <x v="1"/>
+    <n v="3861"/>
+    <x v="110"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="159"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="7927"/>
+    <x v="111"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="160"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="6162"/>
+    <x v="112"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="161"/>
+    <x v="6"/>
+    <x v="1"/>
+    <n v="5523"/>
+    <x v="113"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="162"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="5936"/>
+    <x v="113"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="163"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="7251"/>
+    <x v="114"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="164"/>
+    <x v="4"/>
+    <x v="1"/>
+    <n v="6187"/>
+    <x v="115"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="165"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="3210"/>
+    <x v="116"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="166"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="682"/>
+    <x v="116"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="167"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="793"/>
+    <x v="117"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="168"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="5346"/>
+    <x v="118"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="169"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="7103"/>
+    <x v="119"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="170"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="4603"/>
+    <x v="120"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="171"/>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="8160"/>
+    <x v="121"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="172"/>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="7171"/>
+    <x v="122"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="173"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="3552"/>
+    <x v="122"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="174"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="7273"/>
+    <x v="123"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="175"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="2402"/>
+    <x v="124"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="176"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="1197"/>
+    <x v="124"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="177"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="5015"/>
+    <x v="124"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="178"/>
+    <x v="4"/>
+    <x v="1"/>
+    <n v="5818"/>
+    <x v="125"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="179"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="4399"/>
+    <x v="126"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="180"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="3011"/>
+    <x v="126"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="181"/>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="4715"/>
+    <x v="127"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="182"/>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="5321"/>
+    <x v="128"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="183"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="8894"/>
+    <x v="129"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="184"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="4846"/>
+    <x v="130"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="185"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="284"/>
+    <x v="130"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="186"/>
+    <x v="4"/>
+    <x v="1"/>
+    <n v="8283"/>
+    <x v="131"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="187"/>
+    <x v="4"/>
+    <x v="1"/>
+    <n v="9990"/>
+    <x v="132"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="188"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="9014"/>
+    <x v="132"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="189"/>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="1942"/>
+    <x v="133"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="190"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="7223"/>
+    <x v="134"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="191"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="4673"/>
+    <x v="135"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="192"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="9104"/>
+    <x v="136"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="193"/>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="6078"/>
+    <x v="137"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="194"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="3278"/>
+    <x v="138"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="195"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="136"/>
+    <x v="139"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="196"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="8377"/>
+    <x v="139"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="197"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="2382"/>
+    <x v="139"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="198"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="8702"/>
+    <x v="140"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="199"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="5021"/>
+    <x v="141"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="200"/>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="1760"/>
+    <x v="141"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="201"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="4766"/>
+    <x v="142"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="202"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="1541"/>
+    <x v="143"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="203"/>
+    <x v="4"/>
+    <x v="1"/>
+    <n v="2782"/>
+    <x v="144"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="204"/>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="2455"/>
+    <x v="144"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="205"/>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="4512"/>
+    <x v="145"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="206"/>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="8752"/>
+    <x v="145"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="207"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="9127"/>
+    <x v="146"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="208"/>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="1777"/>
+    <x v="147"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="209"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="680"/>
+    <x v="147"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="210"/>
+    <x v="4"/>
+    <x v="1"/>
+    <n v="958"/>
+    <x v="148"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="211"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="2613"/>
+    <x v="148"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="212"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="339"/>
+    <x v="149"/>
+    <x v="4"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{720BA970-C684-A041-B86E-6F820D6561FB}" name="PivotTable5" cacheId="27" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
+  <location ref="A3:I12" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="6">
+    <pivotField compact="0" outline="0" showAll="0">
+      <items count="214">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+      <items count="8">
+        <item x="5"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" compact="0" numFmtId="164" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="14" outline="0" showAll="0"/>
+    <pivotField axis="axisCol" compact="0" outline="0" showAll="0">
+      <items count="8">
+        <item x="4"/>
+        <item x="2"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="8">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="5"/>
+  </colFields>
+  <colItems count="8">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Amount" fld="3" baseField="0" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7C228ACD-5923-8B4F-B1F9-C28D61FDF3E1}" name="PivotTable6" cacheId="27" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0" chartFormat="6">
+  <location ref="A1:F9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="6">
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisCol" compact="0" outline="0" showAll="0">
+      <items count="8">
+        <item x="5"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" compact="0" numFmtId="164" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="14" outline="0" showAll="0">
+      <items count="151">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+      <items count="8">
+        <item x="4"/>
+        <item x="2"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="1"/>
+  </colFields>
+  <colItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Amount" fld="3" baseField="0" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <chartFormats count="35">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="7" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="9" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="10" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="11" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="12" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="13" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="7" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="9" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="10" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="11" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="12" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="13" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="4" type="dateBetween" evalOrder="-1" id="16" name="Date">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <customFilters and="1">
+            <customFilter operator="greaterThanOrEqual" val="45444"/>
+            <customFilter operator="lessThanOrEqual" val="45473"/>
+          </customFilters>
+        </filterColumn>
+      </autoFilter>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{0605FD5F-26C8-4aeb-8148-2DB25E43C511}">
+          <x15:pivotFilter useWholeDay="1"/>
+        </ext>
+      </extLst>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -469,22 +5225,40 @@
 </a:theme>
 </file>
 
+<file path=xl/timelineCaches/timelineCache1.xml><?xml version="1.0" encoding="utf-8"?>
+<timelineCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="xr10" name="NativeTimeline_Date" xr10:uid="{0DE18A4B-ED53-394A-BEB8-C0F2D5E761C2}" sourceName="Date">
+  <pivotTables>
+    <pivotTable tabId="4" name="PivotTable6"/>
+  </pivotTables>
+  <state minimalRefreshVersion="6" lastRefreshVersion="6" pivotCacheId="923316403" filterType="dateBetween">
+    <selection startDate="2024-06-01T00:00:00" endDate="2024-06-30T00:00:00"/>
+    <bounds startDate="2024-01-01T00:00:00" endDate="2025-01-01T00:00:00"/>
+  </state>
+</timelineCacheDefinition>
+</file>
+
+<file path=xl/timelines/timeline1.xml><?xml version="1.0" encoding="utf-8"?>
+<timelines xmlns="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
+  <timeline name="Date" xr10:uid="{780E1D36-D7A0-5044-87C4-5AC7232EBF3A}" cache="NativeTimeline_Date" caption="Date" level="2" selectionLevel="2" scrollPosition="2024-01-01T00:00:00"/>
+</timelines>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F214"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.44140625" customWidth="1"/>
+    <col min="6" max="6" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.5" customWidth="1"/>
     <col min="8" max="8" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
@@ -504,7 +5278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -524,7 +5298,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -544,7 +5318,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -564,7 +5338,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -584,7 +5358,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -604,7 +5378,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -624,7 +5398,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -644,7 +5418,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -664,7 +5438,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -684,7 +5458,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -704,7 +5478,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -724,7 +5498,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -744,7 +5518,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -764,7 +5538,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -784,7 +5558,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -804,7 +5578,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -824,7 +5598,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -844,7 +5618,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -864,7 +5638,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -884,7 +5658,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -904,7 +5678,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -924,7 +5698,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -944,7 +5718,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -964,7 +5738,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -984,7 +5758,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1004,7 +5778,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1024,7 +5798,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1044,7 +5818,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1064,7 +5838,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1084,7 +5858,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1104,7 +5878,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1124,7 +5898,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1144,7 +5918,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1164,7 +5938,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1184,7 +5958,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1204,7 +5978,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1224,7 +5998,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1244,7 +6018,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1264,7 +6038,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1284,7 +6058,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1304,7 +6078,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
@@ -1324,7 +6098,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>42</v>
       </c>
@@ -1344,7 +6118,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>43</v>
       </c>
@@ -1364,7 +6138,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>44</v>
       </c>
@@ -1384,7 +6158,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>45</v>
       </c>
@@ -1404,7 +6178,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>46</v>
       </c>
@@ -1424,7 +6198,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>47</v>
       </c>
@@ -1444,7 +6218,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>48</v>
       </c>
@@ -1464,7 +6238,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>49</v>
       </c>
@@ -1484,7 +6258,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>50</v>
       </c>
@@ -1504,7 +6278,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>51</v>
       </c>
@@ -1524,7 +6298,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>52</v>
       </c>
@@ -1544,7 +6318,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>53</v>
       </c>
@@ -1564,7 +6338,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>54</v>
       </c>
@@ -1584,7 +6358,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>55</v>
       </c>
@@ -1604,7 +6378,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>56</v>
       </c>
@@ -1624,7 +6398,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>57</v>
       </c>
@@ -1644,7 +6418,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>58</v>
       </c>
@@ -1664,7 +6438,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>59</v>
       </c>
@@ -1684,7 +6458,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>60</v>
       </c>
@@ -1704,7 +6478,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>61</v>
       </c>
@@ -1724,7 +6498,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>62</v>
       </c>
@@ -1744,7 +6518,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>63</v>
       </c>
@@ -1764,7 +6538,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>64</v>
       </c>
@@ -1784,7 +6558,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>65</v>
       </c>
@@ -1804,7 +6578,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>66</v>
       </c>
@@ -1824,7 +6598,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>67</v>
       </c>
@@ -1844,7 +6618,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>68</v>
       </c>
@@ -1864,7 +6638,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>69</v>
       </c>
@@ -1884,7 +6658,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>70</v>
       </c>
@@ -1904,7 +6678,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>71</v>
       </c>
@@ -1924,7 +6698,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>72</v>
       </c>
@@ -1944,7 +6718,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>73</v>
       </c>
@@ -1964,7 +6738,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>74</v>
       </c>
@@ -1984,7 +6758,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>75</v>
       </c>
@@ -2004,7 +6778,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>76</v>
       </c>
@@ -2024,7 +6798,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>77</v>
       </c>
@@ -2044,7 +6818,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>78</v>
       </c>
@@ -2064,7 +6838,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>79</v>
       </c>
@@ -2084,7 +6858,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>80</v>
       </c>
@@ -2104,7 +6878,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>81</v>
       </c>
@@ -2124,7 +6898,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>82</v>
       </c>
@@ -2144,7 +6918,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>83</v>
       </c>
@@ -2164,7 +6938,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>84</v>
       </c>
@@ -2184,7 +6958,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>85</v>
       </c>
@@ -2204,7 +6978,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>86</v>
       </c>
@@ -2224,7 +6998,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>87</v>
       </c>
@@ -2244,7 +7018,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>88</v>
       </c>
@@ -2264,7 +7038,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>89</v>
       </c>
@@ -2284,7 +7058,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>90</v>
       </c>
@@ -2304,7 +7078,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>91</v>
       </c>
@@ -2324,7 +7098,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>92</v>
       </c>
@@ -2344,7 +7118,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>93</v>
       </c>
@@ -2364,7 +7138,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>94</v>
       </c>
@@ -2384,7 +7158,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>95</v>
       </c>
@@ -2404,7 +7178,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>96</v>
       </c>
@@ -2424,7 +7198,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>97</v>
       </c>
@@ -2444,7 +7218,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>98</v>
       </c>
@@ -2464,7 +7238,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>99</v>
       </c>
@@ -2484,7 +7258,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>100</v>
       </c>
@@ -2504,7 +7278,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>101</v>
       </c>
@@ -2524,7 +7298,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>102</v>
       </c>
@@ -2544,7 +7318,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>103</v>
       </c>
@@ -2564,7 +7338,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>104</v>
       </c>
@@ -2584,7 +7358,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>105</v>
       </c>
@@ -2604,7 +7378,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>106</v>
       </c>
@@ -2624,7 +7398,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>107</v>
       </c>
@@ -2644,7 +7418,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>108</v>
       </c>
@@ -2664,7 +7438,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>109</v>
       </c>
@@ -2684,7 +7458,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>110</v>
       </c>
@@ -2704,7 +7478,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>111</v>
       </c>
@@ -2724,7 +7498,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>112</v>
       </c>
@@ -2744,7 +7518,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>113</v>
       </c>
@@ -2764,7 +7538,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>114</v>
       </c>
@@ -2784,7 +7558,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>115</v>
       </c>
@@ -2804,7 +7578,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>116</v>
       </c>
@@ -2824,7 +7598,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>117</v>
       </c>
@@ -2844,7 +7618,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>118</v>
       </c>
@@ -2864,7 +7638,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>119</v>
       </c>
@@ -2884,7 +7658,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>120</v>
       </c>
@@ -2904,7 +7678,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>121</v>
       </c>
@@ -2924,7 +7698,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>122</v>
       </c>
@@ -2944,7 +7718,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>123</v>
       </c>
@@ -2964,7 +7738,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>124</v>
       </c>
@@ -2984,7 +7758,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>125</v>
       </c>
@@ -3004,7 +7778,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>126</v>
       </c>
@@ -3024,7 +7798,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>127</v>
       </c>
@@ -3044,7 +7818,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>128</v>
       </c>
@@ -3064,7 +7838,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>129</v>
       </c>
@@ -3084,7 +7858,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>130</v>
       </c>
@@ -3104,7 +7878,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>131</v>
       </c>
@@ -3124,7 +7898,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>132</v>
       </c>
@@ -3144,7 +7918,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>133</v>
       </c>
@@ -3164,7 +7938,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>134</v>
       </c>
@@ -3184,7 +7958,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>135</v>
       </c>
@@ -3204,7 +7978,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>136</v>
       </c>
@@ -3224,7 +7998,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>137</v>
       </c>
@@ -3244,7 +8018,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>138</v>
       </c>
@@ -3264,7 +8038,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>139</v>
       </c>
@@ -3284,7 +8058,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>140</v>
       </c>
@@ -3304,7 +8078,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>141</v>
       </c>
@@ -3324,7 +8098,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>142</v>
       </c>
@@ -3344,7 +8118,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>143</v>
       </c>
@@ -3364,7 +8138,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>144</v>
       </c>
@@ -3384,7 +8158,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A146">
         <v>145</v>
       </c>
@@ -3404,7 +8178,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A147">
         <v>146</v>
       </c>
@@ -3424,7 +8198,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A148">
         <v>147</v>
       </c>
@@ -3444,7 +8218,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>148</v>
       </c>
@@ -3464,7 +8238,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A150">
         <v>149</v>
       </c>
@@ -3484,7 +8258,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>150</v>
       </c>
@@ -3504,7 +8278,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A152">
         <v>151</v>
       </c>
@@ -3524,7 +8298,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A153">
         <v>152</v>
       </c>
@@ -3544,7 +8318,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>153</v>
       </c>
@@ -3564,7 +8338,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A155">
         <v>154</v>
       </c>
@@ -3584,7 +8358,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A156">
         <v>155</v>
       </c>
@@ -3604,7 +8378,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A157">
         <v>156</v>
       </c>
@@ -3624,7 +8398,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A158">
         <v>157</v>
       </c>
@@ -3644,7 +8418,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A159">
         <v>158</v>
       </c>
@@ -3664,7 +8438,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A160">
         <v>159</v>
       </c>
@@ -3684,7 +8458,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A161">
         <v>160</v>
       </c>
@@ -3704,7 +8478,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>161</v>
       </c>
@@ -3724,7 +8498,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>162</v>
       </c>
@@ -3744,7 +8518,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>163</v>
       </c>
@@ -3764,7 +8538,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>164</v>
       </c>
@@ -3784,7 +8558,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A166">
         <v>165</v>
       </c>
@@ -3804,7 +8578,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A167">
         <v>166</v>
       </c>
@@ -3824,7 +8598,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A168">
         <v>167</v>
       </c>
@@ -3844,7 +8618,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A169">
         <v>168</v>
       </c>
@@ -3864,7 +8638,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A170">
         <v>169</v>
       </c>
@@ -3884,7 +8658,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A171">
         <v>170</v>
       </c>
@@ -3904,7 +8678,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A172">
         <v>171</v>
       </c>
@@ -3924,7 +8698,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A173">
         <v>172</v>
       </c>
@@ -3944,7 +8718,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A174">
         <v>173</v>
       </c>
@@ -3964,7 +8738,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A175">
         <v>174</v>
       </c>
@@ -3984,7 +8758,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A176">
         <v>175</v>
       </c>
@@ -4004,7 +8778,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A177">
         <v>176</v>
       </c>
@@ -4024,7 +8798,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A178">
         <v>177</v>
       </c>
@@ -4044,7 +8818,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A179">
         <v>178</v>
       </c>
@@ -4064,7 +8838,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A180">
         <v>179</v>
       </c>
@@ -4084,7 +8858,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A181">
         <v>180</v>
       </c>
@@ -4104,7 +8878,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A182">
         <v>181</v>
       </c>
@@ -4124,7 +8898,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A183">
         <v>182</v>
       </c>
@@ -4144,7 +8918,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A184">
         <v>183</v>
       </c>
@@ -4164,7 +8938,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A185">
         <v>184</v>
       </c>
@@ -4184,7 +8958,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A186">
         <v>185</v>
       </c>
@@ -4204,7 +8978,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A187">
         <v>186</v>
       </c>
@@ -4224,7 +8998,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A188">
         <v>187</v>
       </c>
@@ -4244,7 +9018,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A189">
         <v>188</v>
       </c>
@@ -4264,7 +9038,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A190">
         <v>189</v>
       </c>
@@ -4284,7 +9058,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A191">
         <v>190</v>
       </c>
@@ -4304,7 +9078,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A192">
         <v>191</v>
       </c>
@@ -4324,7 +9098,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A193">
         <v>192</v>
       </c>
@@ -4344,7 +9118,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A194">
         <v>193</v>
       </c>
@@ -4364,7 +9138,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A195">
         <v>194</v>
       </c>
@@ -4384,7 +9158,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A196">
         <v>195</v>
       </c>
@@ -4404,7 +9178,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A197">
         <v>196</v>
       </c>
@@ -4424,7 +9198,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A198">
         <v>197</v>
       </c>
@@ -4444,7 +9218,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A199">
         <v>198</v>
       </c>
@@ -4464,7 +9238,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A200">
         <v>199</v>
       </c>
@@ -4484,7 +9258,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A201">
         <v>200</v>
       </c>
@@ -4504,7 +9278,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A202">
         <v>201</v>
       </c>
@@ -4524,7 +9298,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A203">
         <v>202</v>
       </c>
@@ -4544,7 +9318,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A204">
         <v>203</v>
       </c>
@@ -4564,7 +9338,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A205">
         <v>204</v>
       </c>
@@ -4584,7 +9358,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A206">
         <v>205</v>
       </c>
@@ -4604,7 +9378,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A207">
         <v>206</v>
       </c>
@@ -4624,7 +9398,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A208">
         <v>207</v>
       </c>
@@ -4644,7 +9418,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A209">
         <v>208</v>
       </c>
@@ -4664,7 +9438,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A210">
         <v>209</v>
       </c>
@@ -4684,7 +9458,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A211">
         <v>210</v>
       </c>
@@ -4704,7 +9478,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A212">
         <v>211</v>
       </c>
@@ -4724,7 +9498,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A213">
         <v>212</v>
       </c>
@@ -4744,7 +9518,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A214">
         <v>213</v>
       </c>
@@ -4765,6 +9539,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -4772,33 +9547,438 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A3:I12"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.109375" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="8" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1">
+        <v>20634</v>
+      </c>
+      <c r="C5" s="1">
+        <v>24867</v>
+      </c>
+      <c r="D5" s="1">
+        <v>80193</v>
+      </c>
+      <c r="E5" s="1">
+        <v>9082</v>
+      </c>
+      <c r="F5" s="1">
+        <v>10332</v>
+      </c>
+      <c r="G5" s="1">
+        <v>17534</v>
+      </c>
+      <c r="H5" s="1">
+        <v>28615</v>
+      </c>
+      <c r="I5" s="1">
+        <v>191257</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1">
+        <v>52721</v>
+      </c>
+      <c r="C6" s="1">
+        <v>33775</v>
+      </c>
+      <c r="D6" s="1">
+        <v>36094</v>
+      </c>
+      <c r="E6" s="1">
+        <v>39686</v>
+      </c>
+      <c r="F6" s="1">
+        <v>40050</v>
+      </c>
+      <c r="G6" s="1">
+        <v>42908</v>
+      </c>
+      <c r="H6" s="1">
+        <v>95061</v>
+      </c>
+      <c r="I6" s="1">
+        <v>340295</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="1">
+        <v>14433</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1">
+        <v>680</v>
+      </c>
+      <c r="E7" s="1">
+        <v>29905</v>
+      </c>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1">
+        <v>5100</v>
+      </c>
+      <c r="H7" s="1">
+        <v>7163</v>
+      </c>
+      <c r="I7" s="1">
+        <v>57281</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="1">
+        <v>17953</v>
+      </c>
+      <c r="C8" s="1">
+        <v>12407</v>
+      </c>
+      <c r="D8" s="1">
+        <v>5341</v>
+      </c>
+      <c r="E8" s="1">
+        <v>37197</v>
+      </c>
+      <c r="F8" s="1">
+        <v>4390</v>
+      </c>
+      <c r="G8" s="1">
+        <v>38436</v>
+      </c>
+      <c r="H8" s="1">
+        <v>26715</v>
+      </c>
+      <c r="I8" s="1">
+        <v>142439</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="1">
+        <v>8106</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1">
+        <v>9104</v>
+      </c>
+      <c r="E9" s="1">
+        <v>21636</v>
+      </c>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1">
+        <v>41815</v>
+      </c>
+      <c r="H9" s="1">
+        <v>56284</v>
+      </c>
+      <c r="I9" s="1">
+        <v>136945</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1">
+        <v>9186</v>
+      </c>
+      <c r="C10" s="1">
+        <v>3767</v>
+      </c>
+      <c r="D10" s="1">
+        <v>7388</v>
+      </c>
+      <c r="E10" s="1">
+        <v>8775</v>
+      </c>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1">
+        <v>5600</v>
+      </c>
+      <c r="H10" s="1">
+        <v>22363</v>
+      </c>
+      <c r="I10" s="1">
+        <v>57079</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="1">
+        <v>8680</v>
+      </c>
+      <c r="C11" s="1">
+        <v>19929</v>
+      </c>
+      <c r="D11" s="1">
+        <v>2256</v>
+      </c>
+      <c r="E11" s="1">
+        <v>8887</v>
+      </c>
+      <c r="F11" s="1">
+        <v>12010</v>
+      </c>
+      <c r="G11" s="1">
+        <v>21744</v>
+      </c>
+      <c r="H11" s="1">
+        <v>30932</v>
+      </c>
+      <c r="I11" s="1">
+        <v>104438</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="1">
+        <v>131713</v>
+      </c>
+      <c r="C12" s="1">
+        <v>94745</v>
+      </c>
+      <c r="D12" s="1">
+        <v>141056</v>
+      </c>
+      <c r="E12" s="1">
+        <v>155168</v>
+      </c>
+      <c r="F12" s="1">
+        <v>66782</v>
+      </c>
+      <c r="G12" s="1">
+        <v>173137</v>
+      </c>
+      <c r="H12" s="1">
+        <v>267133</v>
+      </c>
+      <c r="I12" s="1">
+        <v>1029734</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.88671875" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" customWidth="1"/>
-    <col min="3" max="3" width="7.44140625" customWidth="1"/>
-    <col min="4" max="4" width="6.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="7.33203125" customWidth="1"/>
-    <col min="7" max="7" width="7.109375" customWidth="1"/>
-    <col min="8" max="8" width="7.44140625" customWidth="1"/>
-    <col min="9" max="9" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1">
+        <v>8891</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1">
+        <v>8891</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1">
+        <v>521</v>
+      </c>
+      <c r="C4" s="1">
+        <v>6941</v>
+      </c>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1">
+        <v>7462</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="1">
+        <v>5605</v>
+      </c>
+      <c r="C5" s="1">
+        <v>107</v>
+      </c>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1">
+        <v>5712</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1">
+        <v>9630</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1">
+        <v>9630</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1">
+        <v>7231</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1">
+        <v>7231</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1">
+        <v>8160</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1">
+        <v>4514</v>
+      </c>
+      <c r="F8" s="1">
+        <v>12674</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="1">
+        <v>6126</v>
+      </c>
+      <c r="C9" s="1">
+        <v>15208</v>
+      </c>
+      <c r="D9" s="1">
+        <v>25752</v>
+      </c>
+      <c r="E9" s="1">
+        <v>4514</v>
+      </c>
+      <c r="F9" s="1">
+        <v>51600</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{7E03D99C-DC04-49d9-9315-930204A7B6E9}">
+      <x15:timelineRefs>
+        <x15:timelineRef r:id="rId3"/>
+      </x15:timelineRefs>
+    </ext>
+  </extLst>
 </worksheet>
 </file>